--- a/tableturf_sim/data/NPCs/统计.xlsx
+++ b/tableturf_sim/data/NPCs/统计.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD833F9-589C-6E4D-B046-82504E318A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="22260" windowHeight="12640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NPC统计" sheetId="1" r:id="rId1"/>
@@ -422,8 +423,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,14 +593,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -612,9 +613,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -905,18 +903,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.125" customWidth="1"/>
-    <col min="5" max="5" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.1640625" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="52" thickBot="1">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -926,7 +924,7 @@
       <c r="C1" s="1">
         <v>0</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="25" t="s">
         <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -936,7 +934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="35" thickBot="1">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -954,7 +952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="35" thickBot="1">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -964,7 +962,7 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="25" t="s">
         <v>94</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -974,7 +972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="52" thickBot="1">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -984,7 +982,7 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="25" t="s">
         <v>95</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -994,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="35" thickBot="1">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1012,7 +1010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="35" thickBot="1">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -1022,7 +1020,7 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="25" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1032,7 +1030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="35" thickBot="1">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -1050,7 +1048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="35" thickBot="1">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -1060,7 +1058,7 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="25" t="s">
         <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1070,7 +1068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="52" thickBot="1">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -1088,7 +1086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="35" thickBot="1">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -1098,7 +1096,7 @@
       <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="25" t="s">
         <v>63</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1108,7 +1106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="35" thickBot="1">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -1126,7 +1124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="35" thickBot="1">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -1136,7 +1134,7 @@
       <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="25" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1146,7 +1144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="35" thickBot="1">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1164,7 +1162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="35" thickBot="1">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -1182,7 +1180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="49" thickBot="1">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -1192,7 +1190,7 @@
       <c r="C15" s="1">
         <v>14</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="25" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1202,7 +1200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="52" thickBot="1">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1220,7 +1218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="35" thickBot="1">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -1238,7 +1236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="18" thickBot="1">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -1256,7 +1254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="35" thickBot="1">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1274,7 +1272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="35" thickBot="1">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -1292,7 +1290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="18" thickBot="1">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -1310,7 +1308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="35" thickBot="1">
       <c r="A22" t="s">
         <v>77</v>
       </c>
@@ -1328,7 +1326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="35" thickBot="1">
       <c r="A23" t="s">
         <v>78</v>
       </c>
@@ -1346,7 +1344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="35" thickBot="1">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -1356,7 +1354,7 @@
       <c r="C24" s="1">
         <v>110</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="25" t="s">
         <v>80</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -1366,7 +1364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="35" thickBot="1">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -1376,7 +1374,7 @@
       <c r="C25" s="1">
         <v>200</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="25" t="s">
         <v>81</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -1386,7 +1384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="35" thickBot="1">
       <c r="A26" t="s">
         <v>83</v>
       </c>
@@ -1396,7 +1394,7 @@
       <c r="C26" s="1">
         <v>201</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="25" t="s">
         <v>84</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -1406,7 +1404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="35" thickBot="1">
       <c r="A27" t="s">
         <v>85</v>
       </c>
@@ -1416,7 +1414,7 @@
       <c r="C27" s="1">
         <v>202</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="25" t="s">
         <v>86</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -1426,7 +1424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="49" thickBot="1">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -1436,7 +1434,7 @@
       <c r="C28" s="1">
         <v>203</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="25" t="s">
         <v>88</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -1446,7 +1444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="35" thickBot="1">
       <c r="A29" t="s">
         <v>89</v>
       </c>
@@ -1456,7 +1454,7 @@
       <c r="C29" s="1">
         <v>204</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="25" t="s">
         <v>90</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -1466,7 +1464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="35" thickBot="1">
       <c r="A30" t="s">
         <v>91</v>
       </c>
@@ -1476,7 +1474,7 @@
       <c r="C30" s="1">
         <v>205</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="25" t="s">
         <v>92</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1494,15 +1492,12 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="15" customHeight="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -1511,7 +1506,7 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="22"/>
+      <c r="I1" s="19"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -1521,7 +1516,7 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="15" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1540,7 +1535,7 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="15" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1559,7 +1554,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="15" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1578,7 +1573,7 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="15" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1597,7 +1592,7 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
     </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1616,12 +1611,12 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+    <row r="7" spans="1:17" ht="15" customHeight="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -1629,18 +1624,18 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -1648,18 +1643,18 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" ht="15" customHeight="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -1667,18 +1662,18 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+    </row>
+    <row r="10" spans="1:17" ht="15" customHeight="1">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
@@ -1686,18 +1681,18 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="1:17" ht="15" customHeight="1">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
@@ -1705,18 +1700,18 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-    </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" ht="15" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -1724,13 +1719,13 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-    </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -1749,7 +1744,7 @@
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1768,7 +1763,7 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="15" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -1787,7 +1782,7 @@
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1806,7 +1801,7 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="15" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1825,7 +1820,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="15" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1851,17 +1846,14 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
+    <row r="1" spans="1:14" ht="15" customHeight="1">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -1875,9 +1867,9 @@
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
+    <row r="2" spans="1:14" ht="15" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
@@ -1891,9 +1883,9 @@
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
+    <row r="3" spans="1:14" ht="15" customHeight="1">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -1907,9 +1899,9 @@
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
+    <row r="4" spans="1:14" ht="15" customHeight="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -1923,9 +1915,9 @@
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
+    <row r="5" spans="1:14" ht="15" customHeight="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1939,11 +1931,11 @@
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -1955,11 +1947,11 @@
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -1971,13 +1963,13 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -1987,13 +1979,13 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -2003,15 +1995,15 @@
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -2019,15 +2011,15 @@
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -2035,7 +2027,7 @@
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="15" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -2044,14 +2036,14 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -2060,14 +2052,14 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -2078,12 +2070,12 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2094,12 +2086,12 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2112,10 +2104,10 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-    </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2128,10 +2120,10 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-    </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="10"/>
@@ -2144,10 +2136,10 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-    </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2160,10 +2152,10 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-    </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2176,8 +2168,8 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2186,12 +2178,12 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="15" customHeight="1">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="2"/>
@@ -2210,7 +2202,7 @@
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="15" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="2"/>
@@ -2229,7 +2221,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="15" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="2"/>
@@ -2248,7 +2240,7 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="15" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2267,7 +2259,7 @@
       <c r="P4" s="14"/>
       <c r="Q4" s="14"/>
     </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="15" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2286,7 +2278,7 @@
       <c r="P5" s="14"/>
       <c r="Q5" s="14"/>
     </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="15" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2305,7 +2297,7 @@
       <c r="P6" s="14"/>
       <c r="Q6" s="14"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="15" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2324,7 +2316,7 @@
       <c r="P7" s="14"/>
       <c r="Q7" s="14"/>
     </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="15" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2343,7 +2335,7 @@
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
     </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="15" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2362,7 +2354,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2381,7 +2373,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" ht="15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2400,7 +2392,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2419,7 +2411,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2438,7 +2430,7 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2457,7 +2449,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="15" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="2"/>
@@ -2476,7 +2468,7 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="2"/>
@@ -2495,7 +2487,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="15" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="2"/>
@@ -2521,15 +2513,12 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -2542,7 +2531,7 @@
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -2555,7 +2544,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="15" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2568,7 +2557,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="15" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2581,7 +2570,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2594,7 +2583,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -2607,20 +2596,20 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="7"/>
-      <c r="B7" s="23"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="23"/>
+      <c r="F7" s="20"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="23"/>
+      <c r="J7" s="20"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -2633,20 +2622,20 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="23"/>
+      <c r="H9" s="20"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -2659,20 +2648,20 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="15" customHeight="1">
       <c r="A11" s="7"/>
-      <c r="B11" s="23"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="23"/>
+      <c r="F11" s="20"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="23"/>
+      <c r="J11" s="20"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="15" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -2685,20 +2674,20 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="20"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="23"/>
+      <c r="H13" s="20"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -2711,20 +2700,20 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="15" customHeight="1">
       <c r="A15" s="7"/>
-      <c r="B15" s="23"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="23"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="23"/>
+      <c r="J15" s="20"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="15" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2737,20 +2726,20 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="23"/>
+      <c r="D17" s="20"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="23"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="15" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2763,20 +2752,20 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="15" customHeight="1">
       <c r="A19" s="7"/>
-      <c r="B19" s="23"/>
+      <c r="B19" s="20"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="23"/>
+      <c r="F19" s="20"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="23"/>
+      <c r="J19" s="20"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="15" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2789,7 +2778,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="15" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2802,7 +2791,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="15" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2815,7 +2804,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="15" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2828,7 +2817,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="15" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2841,7 +2830,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="15" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2861,15 +2850,12 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15" customHeight="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -2881,7 +2867,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -2893,7 +2879,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2905,7 +2891,7 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="15" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2917,7 +2903,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2929,7 +2915,7 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -2941,7 +2927,7 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -2953,7 +2939,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="15" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -2965,7 +2951,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -2977,7 +2963,7 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -2989,7 +2975,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="15" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -3001,7 +2987,7 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -3013,7 +2999,7 @@
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3025,7 +3011,7 @@
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -3037,7 +3023,7 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -3049,7 +3035,7 @@
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="15" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -3061,7 +3047,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="15" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -3073,7 +3059,7 @@
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="15" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -3085,7 +3071,7 @@
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="15" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -3097,7 +3083,7 @@
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="15" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -3109,7 +3095,7 @@
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="15" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3121,7 +3107,7 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="15" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -3133,7 +3119,7 @@
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="15" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -3145,7 +3131,7 @@
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="15" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -3157,7 +3143,7 @@
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="15" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -3176,15 +3162,12 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="15" customHeight="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -3192,7 +3175,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
-      <c r="H1" s="19"/>
+      <c r="H1" s="8"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -3201,7 +3184,7 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="15" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -3209,7 +3192,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="19"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -3218,7 +3201,7 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="15" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -3226,7 +3209,7 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="19"/>
+      <c r="H3" s="8"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
@@ -3235,7 +3218,7 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="15" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -3243,7 +3226,7 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="19"/>
+      <c r="H4" s="8"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -3252,7 +3235,7 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="15" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -3260,7 +3243,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="19"/>
+      <c r="H5" s="8"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -3269,7 +3252,7 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -3277,7 +3260,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="19"/>
+      <c r="H6" s="8"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -3286,7 +3269,7 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="15" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -3294,7 +3277,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="19"/>
+      <c r="H7" s="8"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -3303,7 +3286,7 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="15" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -3311,7 +3294,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="19"/>
+      <c r="H8" s="8"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -3320,7 +3303,7 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -3328,7 +3311,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="19"/>
+      <c r="H9" s="8"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -3337,7 +3320,7 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -3345,7 +3328,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="19"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -3354,7 +3337,7 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="15" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -3362,7 +3345,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="19"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -3371,7 +3354,7 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="15" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -3379,7 +3362,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="19"/>
+      <c r="H12" s="8"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -3388,7 +3371,7 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3396,7 +3379,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="19"/>
+      <c r="H13" s="8"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -3405,7 +3388,7 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -3413,7 +3396,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="19"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -3422,7 +3405,7 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="15" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -3430,7 +3413,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="19"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -3439,7 +3422,7 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="15" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -3447,7 +3430,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="19"/>
+      <c r="H16" s="8"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -3456,7 +3439,7 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="15" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -3464,7 +3447,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="19"/>
+      <c r="H17" s="8"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
@@ -3473,7 +3456,7 @@
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="15" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -3481,7 +3464,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="19"/>
+      <c r="H18" s="8"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -3497,15 +3480,12 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -3518,7 +3498,7 @@
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -3531,7 +3511,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="15" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -3544,7 +3524,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="15" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -3557,7 +3537,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -3570,7 +3550,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -3583,7 +3563,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -3596,7 +3576,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -3609,7 +3589,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -3622,7 +3602,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -3635,33 +3615,33 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
+    <row r="11" spans="1:11" ht="15" customHeight="1">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1">
+      <c r="A12" s="18"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3674,7 +3654,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -3687,7 +3667,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="15" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -3700,7 +3680,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="15" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -3713,7 +3693,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -3726,7 +3706,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="15" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -3739,7 +3719,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="15" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -3752,7 +3732,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="15" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -3765,7 +3745,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="15" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3778,7 +3758,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="15" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -3798,18 +3778,18 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -3823,7 +3803,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3833,21 +3813,21 @@
       <c r="C2">
         <v>211</v>
       </c>
-      <c r="D2" s="24"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D2" s="21"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>8421504</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="22">
         <v>128128128</v>
       </c>
       <c r="C3">
         <v>9</v>
       </c>
-      <c r="D3" s="26"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3" s="23"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>12611584</v>
       </c>
@@ -3859,7 +3839,7 @@
       </c>
       <c r="D4" s="15"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>15773696</v>
       </c>
@@ -3871,7 +3851,7 @@
       </c>
       <c r="D5" s="16"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>65535</v>
       </c>
@@ -3883,7 +3863,7 @@
       </c>
       <c r="D6" s="12"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>49407</v>
       </c>
@@ -3893,13 +3873,13 @@
       <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" s="27"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" s="24"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>16777215</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="22">
         <v>255255255</v>
       </c>
       <c r="C8" t="s">
@@ -3913,12 +3893,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="15" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3929,7 +3909,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="15" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3940,7 +3920,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="15" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3951,7 +3931,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3962,7 +3942,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -3973,7 +3953,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="15" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -3984,7 +3964,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="15" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -3995,7 +3975,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="15" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4006,7 +3986,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="15" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4017,7 +3997,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4028,7 +4008,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4039,7 +4019,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -4050,7 +4030,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -4061,7 +4041,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -4072,7 +4052,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -4083,7 +4063,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -4094,7 +4074,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -4105,7 +4085,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="15" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -4116,7 +4096,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4127,7 +4107,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="15" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -4138,7 +4118,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="15" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4149,29 +4129,29 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="15" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="5"/>
+      <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="15" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="E23" s="5"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="15" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4182,7 +4162,7 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="15" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4193,7 +4173,7 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="15" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -4211,12 +4191,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:P26"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="15" customHeight="1">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4234,7 +4214,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="15" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4252,7 +4232,7 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="15" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -4270,7 +4250,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="15" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -4288,7 +4268,7 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="15" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4306,7 +4286,7 @@
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="15" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -4324,7 +4304,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="15" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -4342,7 +4322,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
     </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="15" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4360,7 +4340,7 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="15" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4378,7 +4358,7 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4396,7 +4376,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4414,7 +4394,7 @@
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -4432,7 +4412,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -4450,7 +4430,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -4468,7 +4448,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="15" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -4486,7 +4466,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="15" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -4495,16 +4475,16 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+    </row>
+    <row r="17" spans="1:16" ht="15" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -4513,16 +4493,16 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -4531,34 +4511,34 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+    </row>
+    <row r="19" spans="1:16" ht="15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+    </row>
+    <row r="20" spans="1:16" ht="15" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -4576,7 +4556,7 @@
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
     </row>
-    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="15" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4594,7 +4574,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="15" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4612,78 +4592,6 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-    </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-    </row>
-    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-    </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4691,21 +4599,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:S23"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="18"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+    <row r="1" spans="1:19" ht="15" customHeight="1">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
@@ -4713,20 +4618,20 @@
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
     </row>
-    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+    <row r="2" spans="1:19" ht="15" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -4734,20 +4639,20 @@
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
       <c r="S2" s="8"/>
     </row>
-    <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
+    <row r="3" spans="1:19" ht="15" customHeight="1">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -4755,20 +4660,20 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
     </row>
-    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
@@ -4776,20 +4681,20 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
     </row>
-    <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
+    <row r="5" spans="1:19" ht="15" customHeight="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
@@ -4797,20 +4702,20 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
     </row>
-    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
+    <row r="6" spans="1:19" ht="15" customHeight="1">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -4818,20 +4723,20 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
     </row>
-    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
+    <row r="7" spans="1:19" ht="15" customHeight="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -4839,20 +4744,20 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
     </row>
-    <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+    <row r="8" spans="1:19" ht="15" customHeight="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -4860,14 +4765,14 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
     </row>
-    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -4888,7 +4793,7 @@
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
     </row>
-    <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -4909,7 +4814,7 @@
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="15" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -4930,7 +4835,7 @@
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
     </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="15" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -4951,7 +4856,7 @@
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
     </row>
-    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -4972,7 +4877,7 @@
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
     </row>
-    <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -4993,7 +4898,7 @@
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
     </row>
-    <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="15" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -5014,13 +4919,13 @@
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
     </row>
-    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+    <row r="16" spans="1:19" ht="15" customHeight="1">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -5028,20 +4933,20 @@
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
     </row>
-    <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
+    <row r="17" spans="1:19" ht="15" customHeight="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -5049,20 +4954,20 @@
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
     </row>
-    <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
+    <row r="18" spans="1:19" ht="15" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -5070,20 +4975,20 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
       <c r="S18" s="8"/>
     </row>
-    <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
+    <row r="19" spans="1:19" ht="15" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -5091,20 +4996,20 @@
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
     </row>
-    <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
+    <row r="20" spans="1:19" ht="15" customHeight="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -5112,20 +5017,20 @@
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
     </row>
-    <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
+    <row r="21" spans="1:19" ht="15" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -5133,20 +5038,20 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
       <c r="S21" s="8"/>
     </row>
-    <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
+    <row r="22" spans="1:19" ht="15" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -5154,20 +5059,20 @@
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
     </row>
-    <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+    <row r="23" spans="1:19" ht="15" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -5175,8 +5080,8 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="7"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
@@ -5189,77 +5094,74 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+    <row r="1" spans="1:17" ht="15" customHeight="1">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
       <c r="I1" s="7"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-    </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-    </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+    </row>
+    <row r="3" spans="1:17" ht="15" customHeight="1">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-    </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+    </row>
+    <row r="4" spans="1:17" ht="15" customHeight="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -5267,17 +5169,17 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+    </row>
+    <row r="5" spans="1:17" ht="15" customHeight="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -5287,15 +5189,15 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" ht="15" customHeight="1">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
@@ -5307,13 +5209,13 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+    </row>
+    <row r="7" spans="1:17" ht="15" customHeight="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -5327,11 +5229,11 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1">
+      <c r="A8" s="8"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -5347,9 +5249,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="Q8" s="19"/>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -5368,8 +5270,8 @@
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
     </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
+    <row r="10" spans="1:17" ht="15" customHeight="1">
+      <c r="A10" s="8"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -5385,11 +5287,11 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="Q10" s="19"/>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="1:17" ht="15" customHeight="1">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -5403,13 +5305,13 @@
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-    </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" ht="15" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -5421,15 +5323,15 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-    </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" ht="15" customHeight="1">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -5439,15 +5341,15 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -5459,13 +5361,13 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+    </row>
+    <row r="15" spans="1:17" ht="15" customHeight="1">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -5479,11 +5381,11 @@
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" customHeight="1">
+      <c r="A16" s="8"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -5499,9 +5401,9 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
-      <c r="Q16" s="19"/>
-    </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:17" ht="15" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -5520,8 +5422,8 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
+    <row r="18" spans="1:17" ht="15" customHeight="1">
+      <c r="A18" s="8"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -5537,11 +5439,11 @@
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
-      <c r="Q18" s="19"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
+      <c r="Q18" s="8"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -5555,13 +5457,13 @@
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -5573,15 +5475,15 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -5591,17 +5493,17 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -5609,68 +5511,68 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5680,15 +5582,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="15" customHeight="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5706,7 +5605,7 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="15" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5724,7 +5623,7 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="15" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -5742,7 +5641,7 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="15" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -5760,7 +5659,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="15" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5778,7 +5677,7 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -5796,17 +5695,17 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="15" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
@@ -5814,17 +5713,17 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="15" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
@@ -5832,17 +5731,17 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
@@ -5850,17 +5749,17 @@
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -5868,7 +5767,7 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -5886,7 +5785,7 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="15" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -5904,7 +5803,7 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -5922,7 +5821,7 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -5940,7 +5839,7 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="15" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -5958,7 +5857,7 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="15" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -5983,20 +5882,17 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+    <row r="1" spans="1:17" ht="15" customHeight="1">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -6010,12 +5906,12 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+    <row r="2" spans="1:17" ht="15" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -6029,12 +5925,12 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+    <row r="3" spans="1:17" ht="15" customHeight="1">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -6048,12 +5944,12 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+    <row r="4" spans="1:17" ht="15" customHeight="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -6067,12 +5963,12 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+    <row r="5" spans="1:17" ht="15" customHeight="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -6086,12 +5982,12 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
     </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+    <row r="6" spans="1:17" ht="15" customHeight="1">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -6105,12 +6001,12 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+    <row r="7" spans="1:17" ht="15" customHeight="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -6124,12 +6020,12 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
     </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+    <row r="8" spans="1:17" ht="15" customHeight="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -6137,18 +6033,18 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" ht="15" customHeight="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -6156,18 +6052,18 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+    </row>
+    <row r="10" spans="1:17" ht="15" customHeight="1">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
@@ -6175,18 +6071,18 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="1:17" ht="15" customHeight="1">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
@@ -6194,18 +6090,18 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-    </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" ht="15" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -6213,18 +6109,18 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-    </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" ht="15" customHeight="1">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -6232,18 +6128,18 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -6251,18 +6147,18 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+    </row>
+    <row r="15" spans="1:17" ht="15" customHeight="1">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -6270,18 +6166,18 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" customHeight="1">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -6289,18 +6185,18 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-    </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:17" ht="15" customHeight="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -6308,18 +6204,18 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -6327,13 +6223,13 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -6346,13 +6242,13 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -6365,13 +6261,13 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6384,13 +6280,13 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -6403,13 +6299,13 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -6422,13 +6318,13 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -6441,13 +6337,13 @@
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -6460,11 +6356,11 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -6473,15 +6369,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15" customHeight="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6493,7 +6386,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -6505,7 +6398,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -6517,7 +6410,7 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="15" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -6529,7 +6422,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -6541,7 +6434,7 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -6553,7 +6446,7 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -6565,7 +6458,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="15" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10"/>
@@ -6577,7 +6470,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -6589,7 +6482,7 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -6608,15 +6501,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:O15"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="2.5" style="17"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="15" customHeight="1">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6633,7 +6523,7 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="15" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -6650,7 +6540,7 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="15" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -6667,7 +6557,7 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="15" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -6684,7 +6574,7 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="15" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -6701,7 +6591,7 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="15" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -6718,7 +6608,7 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="15" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -6735,7 +6625,7 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="15" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -6752,7 +6642,7 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="15" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -6769,7 +6659,7 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="15" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -6786,7 +6676,7 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="15" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -6803,7 +6693,7 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="15" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -6820,7 +6710,7 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="15" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6837,7 +6727,7 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="15" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -6854,7 +6744,7 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="15" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
